--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92576880641</v>
+        <v>46157.93121954675</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93121954675</v>
+        <v>46157.93187783443</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93187783443</v>
+        <v>46157.93408409882</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93408409882</v>
+        <v>46157.9372612799</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9372612799</v>
+        <v>46158.28223666576</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28223666576</v>
+        <v>46158.29715242753</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29715242753</v>
+        <v>46158.29824038205</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29824038205</v>
+        <v>46158.33394774799</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33394774799</v>
+        <v>46158.36864478728</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36864478728</v>
+        <v>46158.3729545955</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
